--- a/results/link-prediction-gcn/Link/1shot/PubMed/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/PubMed/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.6147±0.1056</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4700±0.0420</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4719±0.0230</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4252±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5006±0.0009</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5078±0.0111</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5078±0.0111</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5078±0.0111</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5522±0.0739</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5388±0.0153</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0183</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5402±0.0593</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5629±0.0889</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4780±0.0153</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.4227±0.0259</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4963±0.0053</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4995±0.0006</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6016±0.0722</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6189±0.0339</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6189±0.0339</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.6189±0.0339</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6197±0.0850</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.7225±0.0019</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.6134±0.0513</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5363±0.0514</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4907±0.0131</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4762±0.0358</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6095±0.0776</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6231±0.0870</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6231±0.0870</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6231±0.0870</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.6133±0.0803</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6932±0.0100</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6848±0.0083</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5360±0.0509</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4908±0.0023</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.4800±0.0134</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5115±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6005±0.0587</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6823±0.0124</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6823±0.0124</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6823±0.0124</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6625±0.0437</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6792±0.0007</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6769±0.0285</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5004±0.0006</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4630±0.0266</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4809±0.0271</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5011±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4495±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.4985±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5583±0.0825</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.6694±0.0153</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6694±0.0153</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6694±0.0153</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5522±0.0738</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7191±0.0071</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.6719±0.0008</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.5757±0.1045</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.5001±0.0032</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.4997±0.0001</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5141±0.0200</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5141±0.0200</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5141±0.0200</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5514±0.0360</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5155±0.0219</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6273±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5002±0.0002</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4997±0.0036</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0143</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4958±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4640±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6697±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6697±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6697±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.6831±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6845±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5889±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4764±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4560±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6027±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.7184±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.7184±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.7184±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.6459±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6937±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7181±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4900±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4958±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.6203±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.6203±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.6203±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7134±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.7044±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4868±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4959±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4868±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4999±0.0001</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5106±0.0066</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5300±0.0000</t>
+          <t>0.5243±0.0039</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5300±0.0000</t>
+          <t>0.5243±0.0039</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5300±0.0000</t>
+          <t>0.5243±0.0039</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5061±0.0029</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6035±0.0000</t>
+          <t>0.5474±0.0216</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5630±0.0000</t>
+          <t>0.5502±0.0072</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.6000±0.1747</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6347±0.0445</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6297±0.0317</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6664±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.5781±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6669±0.0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6699±0.0046</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6699±0.0046</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6699±0.0046</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6875±0.0294</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6744±0.0032</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6945±0.0083</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6036±0.0869</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6902±0.0333</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6216±0.0319</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5667±0.0193</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6583±0.0111</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6660±0.0008</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7127±0.0328</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7212±0.0143</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7212±0.0143</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7212±0.0143</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7225±0.0396</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7775±0.0017</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.7215±0.0261</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3676±0.2764</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6553±0.0160</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6331±0.0394</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7073±0.0302</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7219±0.0392</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7219±0.0392</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7219±0.0392</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.7132±0.0332</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7528±0.0058</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7492±0.0053</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6818±0.0215</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6538±0.0055</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6354±0.0162</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6687±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7113±0.0270</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7496±0.0039</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7496±0.0039</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7496±0.0039</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7388±0.0219</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7419±0.0027</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7477±0.0132</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6669±0.0003</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6178±0.0355</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6397±0.0382</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6896±0.0325</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0070</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0070</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0070</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6873±0.0292</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7720±0.0049</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7491±0.0004</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.4858±0.3331</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.5848±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.6649±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6650±0.0027</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6663±0.0001</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6730±0.0090</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6730±0.0090</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6730±0.0090</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6839±0.0131</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6734±0.0095</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0001</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6572±0.0076</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6516±0.0075</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7256±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6611±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6240±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7455±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7455±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7455±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7510±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7526±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7056±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6368±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6170±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7124±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7688±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7688±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7688±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7293±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7512±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7682±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6541±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6583±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7237±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7237±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7237±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7694±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7637±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6370±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6612±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6514±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6666±0.0001</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6730±0.0000</t>
+          <t>0.6708±0.0025</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6778±0.0000</t>
+          <t>0.6743±0.0015</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6778±0.0000</t>
+          <t>0.6743±0.0015</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6778±0.0000</t>
+          <t>0.6743±0.0015</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6724±0.0000</t>
+          <t>0.6689±0.0010</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7049±0.0000</t>
+          <t>0.6854±0.0087</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6927±0.0000</t>
+          <t>0.6862±0.0028</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2982±0.0000</t>
+          <t>0.7497±0.0556</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8998±0.0000</t>
+          <t>0.8677±0.0294</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5024±0.0000</t>
+          <t>0.5529±0.0601</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6135±0.0000</t>
+          <t>0.6844±0.0146</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.8902±0.0000</t>
+          <t>0.8939±0.0061</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.8870±0.0000</t>
+          <t>0.9113±0.0103</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.8965±0.0000</t>
+          <t>0.8524±0.0343</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9003±0.0000</t>
+          <t>0.8861±0.0216</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9003±0.0000</t>
+          <t>0.8861±0.0216</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9003±0.0000</t>
+          <t>0.8861±0.0216</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8845±0.0000</t>
+          <t>0.8412±0.0362</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6621±0.0000</t>
+          <t>0.6970±0.0183</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8709±0.0000</t>
+          <t>0.7776±0.0132</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6657±0.0000</t>
+          <t>0.5989±0.0094</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8405±0.0000</t>
+          <t>0.8131±0.0121</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5090±0.0000</t>
+          <t>0.6048±0.0743</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.5828±0.0604</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.8508±0.0000</t>
+          <t>0.8443±0.0421</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6849±0.0000</t>
+          <t>0.8675±0.0076</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.9213±0.0000</t>
+          <t>0.8441±0.0166</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9154±0.0241</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9154±0.0241</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.9154±0.0241</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.9390±0.0000</t>
+          <t>0.8766±0.0362</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8350±0.0000</t>
+          <t>0.8620±0.0057</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7625±0.0000</t>
+          <t>0.9210±0.0049</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.3870±0.0000</t>
+          <t>0.6129±0.0455</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.8810±0.0000</t>
+          <t>0.8479±0.0326</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4988±0.0000</t>
+          <t>0.7127±0.0263</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.7287±0.0340</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.8841±0.0000</t>
+          <t>0.8934±0.0072</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.8870±0.0000</t>
+          <t>0.8936±0.0035</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.8342±0.0000</t>
+          <t>0.8212±0.0435</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.8667±0.0000</t>
+          <t>0.8394±0.0128</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.8667±0.0000</t>
+          <t>0.8394±0.0128</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.8667±0.0000</t>
+          <t>0.8394±0.0128</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8280±0.0000</t>
+          <t>0.8331±0.0344</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8513±0.0000</t>
+          <t>0.8378±0.0234</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.8346±0.0000</t>
+          <t>0.7982±0.0077</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6985±0.0000</t>
+          <t>0.6061±0.0584</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8419±0.0000</t>
+          <t>0.8379±0.0248</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4699±0.0000</t>
+          <t>0.6244±0.0924</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5324±0.0000</t>
+          <t>0.6788±0.0119</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.8845±0.0000</t>
+          <t>0.8929±0.0033</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.9022±0.0000</t>
+          <t>0.8960±0.0069</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8634±0.0000</t>
+          <t>0.8455±0.0206</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8771±0.0000</t>
+          <t>0.8602±0.0078</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8771±0.0000</t>
+          <t>0.8602±0.0078</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8771±0.0000</t>
+          <t>0.8602±0.0078</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8372±0.0000</t>
+          <t>0.8297±0.0194</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8189±0.0000</t>
+          <t>0.8127±0.0066</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8523±0.0000</t>
+          <t>0.8267±0.0117</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5582±0.0000</t>
+          <t>0.5629±0.0264</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.8862±0.0000</t>
+          <t>0.8482±0.0314</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4874±0.0000</t>
+          <t>0.6774±0.0176</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6855±0.0000</t>
+          <t>0.7113±0.0272</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.8889±0.0000</t>
+          <t>0.8931±0.0035</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.8926±0.0000</t>
+          <t>0.8992±0.0020</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8747±0.0000</t>
+          <t>0.8387±0.0399</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.8843±0.0000</t>
+          <t>0.8954±0.0087</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.8843±0.0000</t>
+          <t>0.8954±0.0087</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.8843±0.0000</t>
+          <t>0.8954±0.0087</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8703±0.0000</t>
+          <t>0.8309±0.0378</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8672±0.0000</t>
+          <t>0.8688±0.0047</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8279±0.0000</t>
+          <t>0.8501±0.0133</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.2644±0.0000</t>
+          <t>0.6851±0.1532</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.8926±0.0000</t>
+          <t>0.8914±0.0039</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5852±0.0000</t>
+          <t>0.7220±0.0061</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6890±0.0000</t>
+          <t>0.7044±0.0179</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.8858±0.0000</t>
+          <t>0.8900±0.0038</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.8920±0.0000</t>
+          <t>0.8926±0.0036</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8890±0.0000</t>
+          <t>0.8830±0.0093</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.8922±0.0000</t>
+          <t>0.8906±0.0071</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.8922±0.0000</t>
+          <t>0.8906±0.0071</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.8922±0.0000</t>
+          <t>0.8906±0.0071</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8908±0.0000</t>
+          <t>0.8827±0.0100</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6107±0.0000</t>
+          <t>0.7390±0.0375</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.8572±0.0000</t>
+          <t>0.8371±0.0217</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7149±0.0000</t>
+          <t>0.7446±0.0863</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.8841±0.0000</t>
+          <t>0.8701±0.0259</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4958±0.0000</t>
+          <t>0.4998±0.0055</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4868±0.0000</t>
+          <t>0.5048±0.0185</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.8730±0.0000</t>
+          <t>0.8830±0.0054</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.8669±0.0000</t>
+          <t>0.8716±0.0034</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8482±0.0000</t>
+          <t>0.8584±0.0231</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7564±0.0000</t>
+          <t>0.7396±0.0078</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7564±0.0000</t>
+          <t>0.7396±0.0078</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7564±0.0000</t>
+          <t>0.7396±0.0078</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.8432±0.0000</t>
+          <t>0.8635±0.0151</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7374±0.0000</t>
+          <t>0.7370±0.0144</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6990±0.0000</t>
+          <t>0.6854±0.0073</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.3946±0.0000</t>
+          <t>0.7337±0.0400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8810±0.0000</t>
+          <t>0.8540±0.0246</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5011±0.0000</t>
+          <t>0.5574±0.0736</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6152±0.0000</t>
+          <t>0.7332±0.0201</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8742±0.0000</t>
+          <t>0.8781±0.0077</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.8712±0.0000</t>
+          <t>0.8961±0.0132</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8816±0.0000</t>
+          <t>0.8409±0.0277</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.8872±0.0000</t>
+          <t>0.8742±0.0237</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8872±0.0000</t>
+          <t>0.8742±0.0237</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.8872±0.0000</t>
+          <t>0.8742±0.0237</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8673±0.0000</t>
+          <t>0.8336±0.0292</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6878±0.0000</t>
+          <t>0.7266±0.0174</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8653±0.0000</t>
+          <t>0.7637±0.0263</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7049±0.0000</t>
+          <t>0.6719±0.0041</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8649±0.0000</t>
+          <t>0.8309±0.0190</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5046±0.0000</t>
+          <t>0.6230±0.0874</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7013±0.0000</t>
+          <t>0.6146±0.0737</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.8412±0.0000</t>
+          <t>0.8479±0.0188</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6723±0.0000</t>
+          <t>0.8596±0.0016</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.9176±0.0000</t>
+          <t>0.8486±0.0171</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.9078±0.0140</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.9078±0.0140</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.9078±0.0140</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9357±0.0000</t>
+          <t>0.8670±0.0383</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7835±0.0000</t>
+          <t>0.8221±0.0064</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7406±0.0000</t>
+          <t>0.9099±0.0025</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5203±0.0000</t>
+          <t>0.6654±0.0196</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8644±0.0000</t>
+          <t>0.8351±0.0275</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.4994±0.0000</t>
+          <t>0.7381±0.0247</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7398±0.0000</t>
+          <t>0.7740±0.0287</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.8705±0.0000</t>
+          <t>0.8791±0.0086</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8721±0.0000</t>
+          <t>0.8755±0.0035</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.8344±0.0000</t>
+          <t>0.8283±0.0338</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.8706±0.0000</t>
+          <t>0.8363±0.0108</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.8706±0.0000</t>
+          <t>0.8363±0.0108</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.8706±0.0000</t>
+          <t>0.8363±0.0108</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8326±0.0000</t>
+          <t>0.8317±0.0256</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8394±0.0000</t>
+          <t>0.8292±0.0243</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.8307±0.0000</t>
+          <t>0.7842±0.0068</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7168±0.0000</t>
+          <t>0.6558±0.0292</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8510±0.0000</t>
+          <t>0.8347±0.0201</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4847±0.0000</t>
+          <t>0.6558±0.1100</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5271±0.0000</t>
+          <t>0.6902±0.0401</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.8704±0.0000</t>
+          <t>0.8774±0.0026</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.8811±0.0000</t>
+          <t>0.8842±0.0094</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8699±0.0000</t>
+          <t>0.8480±0.0193</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8863±0.0000</t>
+          <t>0.8655±0.0060</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8863±0.0000</t>
+          <t>0.8655±0.0060</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8863±0.0000</t>
+          <t>0.8655±0.0060</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8487±0.0000</t>
+          <t>0.8352±0.0172</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8053±0.0000</t>
+          <t>0.8037±0.0028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8527±0.0000</t>
+          <t>0.8148±0.0177</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.6463±0.0169</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.8689±0.0000</t>
+          <t>0.8422±0.0220</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4936±0.0000</t>
+          <t>0.7124±0.0164</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7148±0.0000</t>
+          <t>0.7561±0.0147</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.8753±0.0000</t>
+          <t>0.8780±0.0045</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8760±0.0000</t>
+          <t>0.8826±0.0053</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.8645±0.0000</t>
+          <t>0.8341±0.0299</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.8852±0.0000</t>
+          <t>0.8976±0.0061</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.8852±0.0000</t>
+          <t>0.8976±0.0061</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.8852±0.0000</t>
+          <t>0.8976±0.0061</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8622±0.0000</t>
+          <t>0.8285±0.0293</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8498±0.0000</t>
+          <t>0.8456±0.0050</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8174±0.0000</t>
+          <t>0.8413±0.0163</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.3718±0.0000</t>
+          <t>0.6912±0.0914</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.8695±0.0000</t>
+          <t>0.8637±0.0075</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5757±0.0000</t>
+          <t>0.7438±0.0219</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.7422±0.0000</t>
+          <t>0.7530±0.0144</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.8706±0.0000</t>
+          <t>0.8732±0.0041</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8756±0.0000</t>
+          <t>0.8746±0.0039</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8694±0.0000</t>
+          <t>0.8607±0.0110</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8709±0.0000</t>
+          <t>0.8661±0.0068</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8709±0.0000</t>
+          <t>0.8661±0.0068</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8709±0.0000</t>
+          <t>0.8661±0.0068</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8686±0.0000</t>
+          <t>0.8605±0.0106</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.7600±0.0358</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8351±0.0000</t>
+          <t>0.8212±0.0184</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7263±0.0000</t>
+          <t>0.7343±0.0453</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8681±0.0000</t>
+          <t>0.8547±0.0226</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4979±0.0000</t>
+          <t>0.5000±0.0028</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4935±0.0000</t>
+          <t>0.5033±0.0105</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.8518±0.0000</t>
+          <t>0.8666±0.0063</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.8595±0.0000</t>
+          <t>0.8653±0.0038</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8446±0.0000</t>
+          <t>0.8493±0.0188</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6956±0.0000</t>
+          <t>0.6810±0.0100</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6956±0.0000</t>
+          <t>0.6810±0.0100</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6956±0.0000</t>
+          <t>0.6810±0.0100</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8356±0.0000</t>
+          <t>0.8525±0.0116</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7147±0.0000</t>
+          <t>0.7112±0.0143</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6411±0.0000</t>
+          <t>0.6252±0.0034</t>
         </is>
       </c>
     </row>
